--- a/harbor-weakness/FIN3-WKN-152/tests/__golden_output/FIN3-WKN-152_ipo_model.xlsx
+++ b/harbor-weakness/FIN3-WKN-152/tests/__golden_output/FIN3-WKN-152_ipo_model.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing_Summary" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error_Audit" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source_Trace" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tieout_Detail" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1010,6 +1011,654 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>输入材料清点（脚本 os.walk 实际扫描）</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>文件总数</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>来源目录数</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>目录</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>文件数</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>committee/</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>sec_filings/</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>financials/</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>comps/</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>research/</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>internal/</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>legacy/</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>七目录小计</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>根目录散件（input_files 顶层文件）</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>合计（七目录小计 + 根目录散件 = 文件总数）</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>待核实项</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2024E 分季度收入拆分</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>待核实——材料未载明，不予给出</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序列名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>期间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>明细加总值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>目标年度数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>处置结果</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>依据条款</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>月度收入</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>723.801</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>666.701</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2022-08 重复导出（两行同值 57.100，无标注）</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>重复行去重；666.701 = 723.801 − 57.100</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / Source_Index SEC-01 Priority 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>月度收入</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>801.55</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>804.029</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>-2.479</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2023-12 同月双值（SEC-01 68.979 vs INT-01 66.500，无标注；此处为取 INT-01 值的对照加总）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>按来源优先级取 SEC-01；804.029 = 801.550 + 2.479；SEC-01 Priority 1 &gt; INT-01 Priority 9</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / Source_Index Priority 1 &gt; 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>分部收入</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>666.701</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>666.701</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分部加总与 SEC-01 年度数一致</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / SEC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>分部收入</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>941.252</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>804.029</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>137.223</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Other 分部量级错位</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>941.252 − 152.470 + 15.247 = 804.029</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / SEC-01 年度数差额修正</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>地区收入</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>804.029</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>804.029</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>地区加总与 SEC-01 年度数一致</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / SEC-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SBC 明细合计</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>49.086</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>-0.594</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>文件 TOTAL 行 49.680 与明细加总 49.086 不一致</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>以明细为准取 49.086（撤回 SBC 加回按明细值）</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 / CP-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>cap table 合计</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>143.716563</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>143.716563</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>明细各类别合计与发行条款 pre-money 股数一致</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>CP-10 / Offering_Terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>重构明细合计</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>8.098000000000001</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>8.098000000000001</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>无异常</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>明细与 TOTAL 一致；不重复调整（CP-04）</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>CP-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>钦定勾稽算式（计算结果）</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>666.701 = 723.801 − 57.100</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>钦定勾稽算式（计算结果）</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>804.029 = 801.550 + 2.479</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>钦定勾稽算式（计算结果）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>941.252 − 152.470 + 15.247 = 804.029</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1021,7 +1670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1128,89 +1777,133 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2023 Free Cash Flow</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>-84.83799999999999</v>
-      </c>
+          <t>承销口径 EBITDA 完整算式</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>No normalization</t>
+          <t>-118.361 = -69.275 - 49.086</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>-84.83799999999999</v>
+        <v>-118.361</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Cash quality weak</t>
+          <t>三个列报值齐全：起始值、SBC 加回撤销项、结果</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2023 Restructuring</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>8.098000000000001</v>
-      </c>
+          <t>正负判断</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Non-recurring but already reflected in management Adj EBITDA - no double count (CP-04)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8.098000000000001</v>
-      </c>
+          <t>调整后 EBITDA 仍为负</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>No double count</t>
+          <t>-118.361 &lt; 0，盈利质量弱（CP-05 / CP-13）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2023 Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>-84.83799999999999</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>No normalization</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-84.83799999999999</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Cash quality weak</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>2023 Restructuring</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>8.098000000000001</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Non-recurring but already reflected in management Adj EBITDA - no double count (CP-04)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>8.098000000000001</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>No double count</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t>Valuation method selected</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Underwriting EBITDA remains negative -&gt; EV / 2024E Revenue (CP-05)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>EV / 2024E Revenue</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2024E Revenue = 2023A x (1 + growth)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="n">
+      <c r="E10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024E Revenue 完整算式</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>980.915 = 804.029 × (1 + 22%)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>980.91538</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>USD mm</t>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22% 为 CP-06 委员会内部预测假设，非 SEC 公开事实</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1383,80 +2076,74 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Cross-check</t>
+          <t>净现金桥（分列两行 + 合计算式）</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Committee supported range</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>$31.27 - $37.25</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="n"/>
+          <t>2023 年末现金及现金等价物</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>401.176</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Committee midpoint</t>
+          <t>2023 年末有价证券</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>34.26074180990537</v>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+        <v>811.946</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Proposed Committee Price</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+          <t>净现金合计算式</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1,213.122 = 401.176 + 811.946</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Proposed price vs midpoint</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-0.2607418099053689</v>
-      </c>
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
@@ -1467,12 +2154,10 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Distance within guardrail (&lt;= 0.50)</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="b">
-        <v>1</v>
-      </c>
+          <t>估值链四步算式（逐行列出，每步带列报值）</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
@@ -1483,52 +2168,538 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Proposed-price implied pre-money equity</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>4886.363142</v>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+          <t>档位</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>步骤</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>算式</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>列报值</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>第1步</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>EV = 4.0 × 2024E Revenue 980.915 = 3923.662</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3923.66152</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>第2步</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>pre-money Equity = EV + 401.176 + 811.946 = 5136.784</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>5136.78352</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>第3步</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>每股 = Equity ÷ 143.716563 = 35.7425</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>35.74246010879066</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>第4步</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>折后每股 = 每股 × (1 − 12.5%) = 35.7425 × 0.875 = 31.2747</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>31.27465259519183</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Mid</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>第1步</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EV = 4.5 × 2024E Revenue 980.915 = 4414.119</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4414.11921</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>第2步</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>pre-money Equity = EV + 401.176 + 811.946 = 5627.241</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5627.24121</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>第3步</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>每股 = Equity ÷ 143.716563 = 39.1551</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>39.15513349703471</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>第4步</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>折后每股 = 每股 × (1 − 12.5%) = 39.1551 × 0.875 = 34.2607</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>34.26074180990537</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>第1步</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EV = 5.0 × 2024E Revenue 980.915 = 4904.577</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>4904.5769</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>第2步</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>pre-money Equity = EV + 401.176 + 811.946 = 6117.699</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6117.6989</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>第3步</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>每股 = Equity ÷ 143.716563 = 42.5678</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>42.56780688527877</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>第4步</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>折后每股 = 每股 × (1 − 12.5%) = 42.5678 × 0.875 = 37.2468</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>37.24683102461893</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>执行折扣算式与作用对象</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>折后每股 = 每股 × (1 − 12.5%) = 每股 × 0.875</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>作用对象为 peer-implied 每股价值（per-share），非收入、非企业价值；比例 12.5%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>拟议价定位（三行分列判算）</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>① 区间包含：34.00 ≥ 31.27 且 34.00 ≤ 37.25 → 在支持区间内</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>② 距离算式：34.26 − 34.00 = 0.26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>③ 护栏比较：0.26 ≤ 0.50 → 未超 $0.50/share 护栏</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Cross-check</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Committee supported range</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>$31.27 - $37.25</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Committee midpoint</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>34.26074180990537</v>
+      </c>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Proposed Committee Price</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n"/>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Proposed price vs midpoint</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>-0.2607418099053689</v>
+      </c>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Distance within guardrail (&lt;= 0.50)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Proposed-price implied pre-money equity</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>4886.363142</v>
+      </c>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
           <t>Proposed-price implied EV / 2024E Revenue</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B40" s="2" t="n">
         <v>3.744707460902489</v>
       </c>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n"/>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Preliminary public filing range</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>$31 - $34</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n"/>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1541,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1737,18 +2908,66 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Base case（增长率 × 倍数）</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Scenario grid uses the same net cash bridge, share count and IPO execution discount as the base case.</t>
+          <t>22% × 4.5x = 34.26</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>增长率轴（5 档）</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>18% / 20% / 22% / 24% / 26%</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>倍数轴（5 档）</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>4.0x / 4.3x / 4.5x / 4.8x / 5.0x</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Scenario grid uses the same net cash bridge, share count and IPO execution discount as the base case.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1761,7 +2980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2043,6 +3262,105 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>钦定算式</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>算式（计算结果）</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>公司 gross primary proceeds（含 greenshoe 情景）</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>631.601918 = (15.276527 + 3.3) × 34</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>USD mm</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>greenshoe 不并入 Base，仅 full-exercise 情景</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>费用扣减（承销费与固定费用分列）</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>486.432 = 519.402 - 25.970 - 7.000</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>USD mm</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>基数为公司 primary gross（不含 secondary）；固定费用只扣一次</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>greenshoe 增量净募集资金</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>106.590 = 3.3 × 34 × (1 − 5%)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>USD mm</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>只扣 5% 承销费，不重复扣减固定费用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2054,7 +3372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2236,7 +3554,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pre-cutoff SEC cross-check</t>
+          <t>SEC-02 截止日前独立口径，仅作交叉验证、不作定价主口径</t>
         </is>
       </c>
     </row>
@@ -2259,7 +3577,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Pre-cutoff SEC cross-check</t>
+          <t>SEC-02 截止日前独立口径，仅作交叉验证、不作定价主口径</t>
         </is>
       </c>
     </row>
@@ -2283,6 +3601,82 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>post-money shares x proposed price</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>股本桥算式</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>算式（计算结果）</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Base post-money 股数桥</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>158.993090 = 143.716563 + 15.276527</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>mm shares</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>secondary 不计入总股数（CP-10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Full greenshoe post-money 股数桥</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>162.293090 = 158.993090 + 3.300000</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>mm shares</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>greenshoe 只在 full-exercise 情景并入（CP-11）</t>
         </is>
       </c>
     </row>
@@ -2297,7 +3691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2485,48 +3879,152 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>QoE view</t>
+          <t>负 QoE 前提①</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Underwriting EBITDA remains negative after reversing the SBC addback; 2023 FCF is also negative.</t>
+          <t>承销口径 EBITDA 为负：-118.361mm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Structure view</t>
+          <t>负 QoE 前提②</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Base separates primary from secondary, excludes greenshoe from Base, and grants no secondary proceeds or share count increase to the company.</t>
+          <t>2023 年 FCF 为负：-84.838mm</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Proceed at $34</t>
-        </is>
+          <t>净现金桥-现金及现金等价物</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>401.176</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>净现金桥-有价证券</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>811.946</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>净现金桥-合计算式</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1,213.122 = 401.176 + 811.946</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>拟议价定位①（区间包含）</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>① 区间包含：34.00 ≥ 31.27 且 34.00 ≤ 37.25 → 在支持区间内</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>拟议价定位②（距离）</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>② 距离算式：34.26 − 34.00 = 0.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>拟议价定位③（护栏）</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>③ 护栏比较：0.26 ≤ 0.50 → 未超 $0.50/share 护栏</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Structure view</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Base separates primary from secondary, excludes greenshoe from Base, and grants no secondary proceeds or share count increase to the company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Proceed at $34</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>Disclosure requirement</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Disclose negative QoE in the memo; do not raise the price solely because management Adjusted EBITDA improved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>输入材料清点</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>文件总数 60；来源目录数 7；分目录明细见 Inputs 表</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>数据核验明细</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>四处明细异常（2022-08 重复、2023-12 双值、分部 Other 量级、SBC TOTAL 行不符）逐行见 Tieout_Detail 表</t>
         </is>
       </c>
     </row>
@@ -2541,7 +4039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2884,17 +4382,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Duplicate / unaudited detail rows</t>
+          <t>Unlabelled duplicate / superseded detail rows</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Summed the monthly detail without handling duplicated and unaudited records</t>
+          <t>Summed the monthly detail row-by-row across a file where one month is exported twice and another month carries two different values from different sources</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>De-duplicate and exclude unaudited records, then tie out to SEC-01</t>
+          <t>De-duplicate identical re-exports, resolve same-month conflicts by Source_Index Priority, then tie out to the SEC-01 annual figure</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2909,58 +4407,78 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>Segment magnitude error</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Consumed the segment extract at face value even though the Other segment is an order of magnitude too large and the parts overshoot the SEC-01 annual revenue</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Rebuild the Other segment as the annual figure less the Advertising segment</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Restores the segment split without disturbing the annual tie-out</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SBC total row mismatch</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Took the detail file's TOTAL row instead of re-summing the components</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Re-sum the SBC components and flag the total row as inconsistent</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>The underwriting EBITDA add-back follows the components, not the stale total</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>Fact vs assumption labelling</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Treated the 22% growth, peer multiples and 12.5% discount as SEC public facts</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Label them as internal committee assumptions</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Separates facts from assumptions</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Total issues identified and corrected: 14</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-    </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Information set</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>As-of 2024-03-20: SEC facts and internal committee assumptions are labelled separately throughout the model.</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
@@ -2968,17 +4486,47 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Cross-check</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Monthly detail ties to SEC-01 only after removing the duplicated 2022-08 export row and the unaudited 2023-12 flash row.</t>
+          <t>Total issues identified and corrected: 16</t>
         </is>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Information set</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>As-of 2024-03-20: SEC facts and internal committee assumptions are labelled separately throughout the model.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Cross-check</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Monthly detail ties to SEC-01 only after de-duplicating the repeated 2022-08 export and resolving the two competing 2023-12 values by Source_Index Priority.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2991,7 +4539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3031,189 +4579,405 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FY2023 Revenue</t>
+          <t>FY2023 Revenue 取值</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>804.029</t>
+          <t>804.029（SEC-01, Priority 1）</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>SEC-01 (Priority 1)</t>
+          <t>sec_filings/SEC-01_financials_extract.xlsx</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>internal/management_flash_20240319.csv gives a different unreviewed figure; CP-02 excludes internal working drafts as a source</t>
+          <t>internal/management_flash_20240319.csv：Revenue 806.200、Adjusted EBITDA -66.100、SBC 47.300（IR 未复核初稿，INT-01 Priority 9）</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>adopt SEC-01</t>
+          <t>按 CP-02 来源优先级排除未复核 flash，取 SEC-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>FY2023 monthly detail 2023-12</t>
+          <t>FY2023 月度明细 2023-12 同月双值</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>audited-final</t>
+          <t>68.979（SEC-01 Priority 1）</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>financials/monthly_revenue_2022_2023.csv</t>
+          <t>financials/monthly_revenue_2022_2023.csv（2023-12）</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>same file also carries an unaudited-preliminary IR record; CP-02 and the revision log require the audited version</t>
+          <t>66.500（INT-01 Priority 9）</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>exclude unaudited</t>
+          <t>两行均无标注，按 Source_Index 优先级取 SEC-01（SEC-01 Priority 1 &gt; INT-01 Priority 9）；804.029 = 801.550 + 2.479</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>FY2022 monthly detail 2022-08</t>
+          <t>FY2022 月度明细 2022-08 重复导出</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>57.100（保留一行，SEC-01 Priority 1）</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>financials/monthly_revenue_2022_2023.csv</t>
+          <t>financials/monthly_revenue_2022_2023.csv（2022-08）</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>a duplicate-export row is present; counting it breaks the tie-out to SEC-01</t>
+          <t>57.100 / 57.100（两行同值、均无标注）</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>de-duplicate</t>
+          <t>重复行去重；666.701 = 723.801 − 57.100</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Peer EV/Revenue range</t>
+          <t>FY2023 分部 Other 量级错位</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>4.0x-5.0x</t>
+          <t>15.247（按年度数修正）</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Committee_Policy_v3 / Underwriting_Assumptions (CP-07)</t>
+          <t>financials/revenue_by_segment_2022_2023.csv（FY2023 Other）</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>comps/underwriter_B_comps_20240318.csv screens a different 4.2x-5.1x set</t>
+          <t>152.470（底表原值，量级错位）</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>adopt committee peer set</t>
+          <t>按 SEC-01 年度数与 Advertising 差额修正；941.252 − 152.470 + 15.247 = 804.029</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SBC treatment</t>
+          <t>Peer EV/Revenue 区间</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>no addback retained</t>
+          <t>4.0x–5.0x（中点 4.5x，CP-07）</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Committee_Policy_v3 CP-03</t>
+          <t>committee/Committee_Policy_v3_20240320.xlsx / committee/Underwriting_Assumptions_20240320.xlsx</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Committee_Policy_v2 CP-03 retained the addback and is superseded</t>
+          <t>comps/underwriter_B_comps_20240318.csv：4.2x–5.1x（承销商自编）</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>adopt v3</t>
+          <t>承销商自编 comps 按 CP-07 仅作交叉验证，不作定价端点</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Underwriting fee basis</t>
+          <t>Peer 区间竞争值（被取代版本）</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>company primary gross proceeds</t>
+          <t>4.0x–5.0x（v3 现行区间）</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Committee_Policy_v3 CP-12</t>
+          <t>committee/Committee_Policy_v3_20240320.xlsx CP-07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Committee_Policy_v2 CP-12 applied the fee to primary + secondary and is superseded</t>
+          <t>committee/Committee_Policy_v2_20240305.xlsx：3.5x–5.5x</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>adopt v3</t>
+          <t>v2 CP-07 已标 SUPERSEDED 作废，故排除 3.5x–5.5x</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Legacy workpaper</t>
+          <t>委员会政策版本</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>not used as a basis for conclusions</t>
+          <t>Committee_Policy v3（2024-03-20）现行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>committee/Committee_Policy_v3_20240320.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CP-03 Management Adjusted EBITDA 作为起点；SBC 加回暂予保留，待审计确认。；CP-07 Peer EV/NTM Revenue 区间 3.5x–5.5x。；CP-09 IPO discount 暂定 10%。；CP-12 承销费按全部发行股份（含 secondary）的 5% 计提。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>v2 上述条款均标 SUPERSEDED 不再适用；一律以 v3（2024-03-20）为准</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2024E 收入增长率</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>22%（CP-06 委员会内部预测假设，非 SEC 公开事实）</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>committee/Underwriting_Assumptions_20240320.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>research/sector_benchmark.md 行业基准 18%（行业中位）</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>行业基准仅作背景，CP-06 指定 22% 由委员会假设，排除 18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SBC 处置</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>撤销 SBC 加回（承销口径不加回）</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>committee/Committee_Policy_v3_20240320.xlsx CP-03</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>v2 CP-03：SBC 加回暂予保留（SUPERSEDED）</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>采用 v3，撤销加回</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>承销费计提基数</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>公司 primary gross proceeds × 5%</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>committee/Committee_Policy_v3_20240320.xlsx CP-12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>v2 CP-12：按含 secondary 的全部发行股份计提（SUPERSEDED）</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>v2 CP-12 已作废；secondary 不形成公司募集资金，费基不含 secondary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Legacy 旧底稿</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>不作为结论依据</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>legacy/Candidate_Model_v0.xlsx</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>contains #REF! broken links and 11 legacy treatments</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>recompute and correct</t>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>含 #REF! 断链与多类 legacy 错误口径</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>全部重算修正，逐条记入 Error_Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>方法论理由①（Mid 档取 4.5x）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Mid = 委员会 peer 区间 4.0x–5.0x 的中点 4.5x</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CP-07：区间以 Committee_Peer_Set 为准</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>算术中位数 / comps/peer_multiples_history.csv 历史倍数中位数</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CP-07 指定以委员会区间为准，历史倍数中位数不属控制口径，故 Mid 取区间中点而非算术或历史中位数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>方法论理由②（排除未复核 flash）</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>不采用 internal/management_flash_20240319.csv</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CP-02 来源优先级：INT-01 Priority 9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>flash 所载 Revenue 806.200、Adj EBITDA -66.100、SBC 47.300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CP-02：未复核 IR 初稿仅供参考，Priority 9 低于 SEC-01 Priority 1，不得作承销口径结论的取数来源，故排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>方法论理由③（采用 v3 而非 v2）</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>采用 Committee_Policy v3（2024-03-20）</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>committee/Committee_Policy_v3_20240320.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>v2（2024-03-05）CP-03 / CP-07 / CP-09 / CP-12</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>v2 上述条款均标 SUPERSEDED 已作废，v3 为现行控制口径，故采用 v3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>方法论理由④（承销费只计 primary）</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>承销费 = 公司 primary gross proceeds × 5%（CP-12）</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>committee/Committee_Policy_v3_20240320.xlsx CP-12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>含 secondary 的发行股份基数（v2 CP-12，已作废）</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>secondary 属出售股东股份转让、不形成公司募集资金，故费基只含公司 primary gross、不含 secondary</t>
         </is>
       </c>
     </row>
